--- a/mario/test/supporting_files/add_sector_iot_master_filled.xlsx
+++ b/mario/test/supporting_files/add_sector_iot_master_filled.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="10420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="new_ser" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -40,7 +40,10 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,16 +78,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -96,6 +108,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,6 +577,16 @@
           <t>M EUR</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -615,7 +638,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -924,8 +947,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="6.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="6" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="5.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -956,6 +987,58 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>New industry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Reg1</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>0.05*53115504</f>
+        <v/>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>M EUR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MARIO doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>New industry</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reg2</t>
+        </is>
+      </c>
+      <c r="C3" s="5">
+        <f>0.05*1195683</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>M EUR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MARIO doc</t>
         </is>
       </c>
     </row>
@@ -970,8 +1053,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="5.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1007,6 +1099,68 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>New industry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Reg1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Reg2</t>
+        </is>
+      </c>
+      <c r="D2" s="5">
+        <f>0.05*288442</f>
+        <v/>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M EUR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MARIO doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>New industry</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reg2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reg1</t>
+        </is>
+      </c>
+      <c r="D3">
+        <f>0.05*437620</f>
+        <v/>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M EUR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MARIO doc</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1253,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
